--- a/output/2026-summer_立替金精算表.xlsx
+++ b/output/2026-summer_立替金精算表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46256</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="4">
@@ -582,7 +582,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>手土産か補食か要確認</t>
+          <t>補食。昨年台帳でも団子は雑費計上</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>手土産か補食か要確認</t>
+          <t>補食。昨年台帳でも団子は雑費計上</t>
         </is>
       </c>
     </row>
@@ -822,41 +822,74 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>占部</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>星野コーチ</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>夏合宿 コーチ謝礼</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>r010</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>占部立替。日付は要確認。2人目のコーチ分は未計上</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>占部 小計</t>
         </is>
       </c>
-      <c r="E16" s="8">
-        <f>SUM(E15:E15)</f>
+      <c r="E17" s="8">
+        <f>SUM(E15:E16)</f>
         <v/>
       </c>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="D18" s="9" t="inlineStr">
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>立替金 合計（各先生への返金額）</t>
         </is>
       </c>
-      <c r="E18" s="10">
-        <f>E13+E16</f>
+      <c r="E19" s="10">
+        <f>E13+E17</f>
         <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>※ settled=no（未精算）の支出のみを対象としています。</t>
-        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
+        <is>
+          <t>※ settled=no（未精算）の支出のみを対象としています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>※ 追加の立替が判明した場合はこの表を更新すること。</t>
         </is>
